--- a/sample-data/contoh-GL.xlsx
+++ b/sample-data/contoh-GL.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="52">
   <si>
-    <t>PT PNG - General Ledger Report (Contoh/Sample)</t>
+    <t>PT Manufaktur Indonesia Sejahtera - General Ledger Report (Contoh/Sample)</t>
   </si>
   <si>
     <t>Period: 01-12-2025 s/d 31-05-2026</t>

--- a/sample-data/contoh-GL.xlsx
+++ b/sample-data/contoh-GL.xlsx
@@ -8467,10 +8467,10 @@
         <v>0</v>
       </c>
       <c r="G307">
-        <v>309161908</v>
+        <v>-345408959</v>
       </c>
       <c r="H307">
-        <v>-309161908</v>
+        <v>345408959</v>
       </c>
     </row>
   </sheetData>
